--- a/Analysis/Sensitivity_merec_entropy_arms_gemini.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_gemini.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
+          <t>{"HVAC": {"energy_cost": 0.158108, "environmental": 0.134875, "comfort": 0.656105, "practicality": 0.050912}, "Appliance": {"energy_cost": 0.1937, "environmental": 0.042827, "comfort": 0.297641, "practicality": 0.465832}, "Shower": {"energy_cost": 0.249504, "environmental": 0.245981, "comfort": 0.202649, "practicality": 0.301865}}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -490,22 +490,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6020399999999999</v>
+        <v>0.61708</v>
       </c>
       <c r="F2" t="n">
-        <v>0.65228</v>
+        <v>0.6569200000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.69128</v>
+        <v>0.69642</v>
       </c>
       <c r="H2" t="n">
-        <v>0.94256</v>
+        <v>0.92204</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02283999999999997</v>
+        <v>0.05542000000000014</v>
       </c>
       <c r="J2" t="n">
-        <v>0.92888</v>
+        <v>0.9295600000000001</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
+          <t>{"HVAC": {"energy_cost": 0.158108, "environmental": 0.134875, "comfort": 0.656105, "practicality": 0.050912}, "Appliance": {"energy_cost": 0.1937, "environmental": 0.042827, "comfort": 0.297641, "practicality": 0.465832}, "Shower": {"energy_cost": 0.249504, "environmental": 0.245981, "comfort": 0.202649, "practicality": 0.301865}}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6248799999999999</v>
+        <v>0.6725000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.67462</v>
+        <v>0.7138399999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7605999999999999</v>
+        <v>0.78154</v>
       </c>
       <c r="H3" t="n">
-        <v>0.93782</v>
+        <v>0.94256</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02283999999999997</v>
+        <v>0.05542000000000014</v>
       </c>
       <c r="J3" t="n">
-        <v>0.92888</v>
+        <v>0.9295600000000001</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
+          <t>{"HVAC": {"energy_cost": 0.158108, "environmental": 0.134875, "comfort": 0.656105, "practicality": 0.050912}, "Appliance": {"energy_cost": 0.1937, "environmental": 0.042827, "comfort": 0.297641, "practicality": 0.465832}, "Shower": {"energy_cost": 0.249504, "environmental": 0.245981, "comfort": 0.202649, "practicality": 0.301865}}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.92888</v>
+        <v>0.9295600000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9466800000000001</v>
+        <v>0.9471999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9385</v>
+        <v>0.94156</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02283999999999997</v>
+        <v>0.05542000000000014</v>
       </c>
       <c r="J4" t="n">
-        <v>0.92888</v>
+        <v>0.9295600000000001</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +601,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
+          <t>{"HVAC": {"energy_cost": 0.337364, "environmental": 0.314813, "comfort": 0.27764, "practicality": 0.070183}, "Appliance": {"energy_cost": 0.19046, "environmental": 0.466726, "comfort": 0.124032, "practicality": 0.218782}, "Shower": {"energy_cost": 0.333224, "environmental": 0.318153, "comfort": 0.122997, "practicality": 0.225626}}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.16992</v>
+        <v>0.07008</v>
       </c>
       <c r="F5" t="n">
-        <v>0.15538</v>
+        <v>0.0682</v>
       </c>
       <c r="G5" t="n">
-        <v>0.38974</v>
+        <v>0.34462</v>
       </c>
       <c r="H5" t="n">
-        <v>0.70052</v>
+        <v>0.66562</v>
       </c>
       <c r="I5" t="n">
-        <v>0.16968</v>
+        <v>0.21744</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9315999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
+          <t>{"HVAC": {"energy_cost": 0.337364, "environmental": 0.314813, "comfort": 0.27764, "practicality": 0.070183}, "Appliance": {"energy_cost": 0.19046, "environmental": 0.466726, "comfort": 0.124032, "practicality": 0.218782}, "Shower": {"energy_cost": 0.333224, "environmental": 0.318153, "comfort": 0.122997, "practicality": 0.225626}}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3396</v>
+        <v>0.28752</v>
       </c>
       <c r="F6" t="n">
-        <v>0.35702</v>
+        <v>0.31792</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5264800000000001</v>
+        <v>0.47694</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8145200000000001</v>
+        <v>0.79488</v>
       </c>
       <c r="I6" t="n">
-        <v>0.16968</v>
+        <v>0.21744</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9315999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
+          <t>{"HVAC": {"energy_cost": 0.337364, "environmental": 0.314813, "comfort": 0.27764, "practicality": 0.070183}, "Appliance": {"energy_cost": 0.19046, "environmental": 0.466726, "comfort": 0.124032, "practicality": 0.218782}, "Shower": {"energy_cost": 0.333224, "environmental": 0.318153, "comfort": 0.122997, "practicality": 0.225626}}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9315999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9323</v>
+        <v>0.9410399999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.95074</v>
+        <v>0.9620599999999999</v>
       </c>
       <c r="H7" t="n">
         <v>0.9949</v>
       </c>
       <c r="I7" t="n">
-        <v>0.16968</v>
+        <v>0.21744</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9315999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -721,7 +721,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138, "environmental": 0.128, "comfort": 0.663, "practicality": 0.071}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+          <t>{"HVAC": {"energy_cost": 0.158, "environmental": 0.135, "comfort": 0.656, "practicality": 0.051}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -730,22 +730,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.40784</v>
+        <v>0.47076</v>
       </c>
       <c r="F8" t="n">
-        <v>0.42306</v>
+        <v>0.4851200000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.53026</v>
+        <v>0.57336</v>
       </c>
       <c r="H8" t="n">
-        <v>0.83178</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.18462</v>
+        <v>0.13814</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9315999999999999</v>
+        <v>0.9343399999999999</v>
       </c>
     </row>
     <row r="9">
@@ -761,7 +761,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138, "environmental": 0.128, "comfort": 0.663, "practicality": 0.071}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+          <t>{"HVAC": {"energy_cost": 0.158, "environmental": 0.135, "comfort": 0.656, "practicality": 0.051}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -770,22 +770,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.59246</v>
+        <v>0.6089</v>
       </c>
       <c r="F9" t="n">
-        <v>0.62336</v>
+        <v>0.63692</v>
       </c>
       <c r="G9" t="n">
-        <v>0.70056</v>
+        <v>0.7148600000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.914</v>
+        <v>0.9158800000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.18462</v>
+        <v>0.13814</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9315999999999999</v>
+        <v>0.9343399999999999</v>
       </c>
     </row>
     <row r="10">
@@ -801,7 +801,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138, "environmental": 0.128, "comfort": 0.663, "practicality": 0.071}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+          <t>{"HVAC": {"energy_cost": 0.158, "environmental": 0.135, "comfort": 0.656, "practicality": 0.051}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9315999999999999</v>
+        <v>0.9343399999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9410000000000001</v>
+        <v>0.9456599999999999</v>
       </c>
       <c r="G10" t="n">
         <v>0.9436</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9846</v>
+        <v>0.9897</v>
       </c>
       <c r="I10" t="n">
-        <v>0.18462</v>
+        <v>0.13814</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9315999999999999</v>
+        <v>0.9343399999999999</v>
       </c>
     </row>
     <row r="11">
@@ -841,7 +841,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.208, "environmental": 0.044, "comfort": 0.292, "practicality": 0.456}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.193806, "environmental": 0.042957, "comfort": 0.297702, "practicality": 0.465534}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.37434</v>
+        <v>0.35864</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4005</v>
+        <v>0.38822</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52718</v>
+        <v>0.54254</v>
       </c>
       <c r="H11" t="n">
-        <v>0.79694</v>
+        <v>0.7835799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02532000000000001</v>
+        <v>0.04785999999999996</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9350200000000001</v>
+        <v>0.90838</v>
       </c>
     </row>
     <row r="12">
@@ -881,7 +881,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.208, "environmental": 0.044, "comfort": 0.292, "practicality": 0.456}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.193806, "environmental": 0.042957, "comfort": 0.297702, "practicality": 0.465534}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.39966</v>
+        <v>0.4065</v>
       </c>
       <c r="F12" t="n">
-        <v>0.43108</v>
+        <v>0.4359</v>
       </c>
       <c r="G12" t="n">
-        <v>0.58446</v>
+        <v>0.58156</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8331200000000001</v>
+        <v>0.8061400000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02532000000000001</v>
+        <v>0.04785999999999996</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9350200000000001</v>
+        <v>0.90838</v>
       </c>
     </row>
     <row r="13">
@@ -921,7 +921,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.208, "environmental": 0.044, "comfort": 0.292, "practicality": 0.456}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.193806, "environmental": 0.042957, "comfort": 0.297702, "practicality": 0.465534}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -930,22 +930,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9350200000000001</v>
+        <v>0.90838</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9436</v>
+        <v>0.92052</v>
       </c>
       <c r="G13" t="n">
-        <v>0.94156</v>
+        <v>0.9169</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02532000000000001</v>
+        <v>0.04785999999999996</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9350200000000001</v>
+        <v>0.90838</v>
       </c>
     </row>
     <row r="14">
@@ -961,7 +961,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.24975, "environmental": 0.245754, "comfort": 0.202797, "practicality": 0.301698}}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.17196</v>
+        <v>0.14528</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1754</v>
+        <v>0.15076</v>
       </c>
       <c r="G14" t="n">
-        <v>0.35794</v>
+        <v>0.37642</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7087</v>
+        <v>0.6872</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08056000000000005</v>
+        <v>0.10872</v>
       </c>
       <c r="J14" t="n">
-        <v>0.90906</v>
+        <v>0.8694000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.24975, "environmental": 0.245754, "comfort": 0.202797, "practicality": 0.301698}}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.25252</v>
+        <v>0.254</v>
       </c>
       <c r="F15" t="n">
-        <v>0.27618</v>
+        <v>0.28306</v>
       </c>
       <c r="G15" t="n">
-        <v>0.44974</v>
+        <v>0.43488</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7823800000000001</v>
+        <v>0.76308</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08056000000000005</v>
+        <v>0.10872</v>
       </c>
       <c r="J15" t="n">
-        <v>0.90906</v>
+        <v>0.8694000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.24975, "environmental": 0.245754, "comfort": 0.202797, "practicality": 0.301698}}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.90906</v>
+        <v>0.8694000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9318</v>
+        <v>0.8964000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.91586</v>
+        <v>0.88412</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.9897</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08056000000000005</v>
+        <v>0.10872</v>
       </c>
       <c r="J16" t="n">
-        <v>0.90906</v>
+        <v>0.8694000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
+          <t>{"HVAC": {"energy_cost": 0.337, "environmental": 0.315, "comfort": 0.278, "practicality": 0.07}, "Appliance": {"energy_cost": 0.19, "environmental": 0.467, "comfort": 0.124, "practicality": 0.219}, "Shower": {"energy_cost": 0.333, "environmental": 0.318, "comfort": 0.123, "practicality": 0.226}}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.16992</v>
+        <v>0.06734</v>
       </c>
       <c r="F17" t="n">
-        <v>0.15538</v>
+        <v>0.06616</v>
       </c>
       <c r="G17" t="n">
-        <v>0.38974</v>
+        <v>0.34462</v>
       </c>
       <c r="H17" t="n">
-        <v>0.70052</v>
+        <v>0.66562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.16968</v>
+        <v>0.22426</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9282</v>
       </c>
     </row>
     <row r="18">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
+          <t>{"HVAC": {"energy_cost": 0.337, "environmental": 0.315, "comfort": 0.278, "practicality": 0.07}, "Appliance": {"energy_cost": 0.19, "environmental": 0.467, "comfort": 0.124, "practicality": 0.219}, "Shower": {"energy_cost": 0.333, "environmental": 0.318, "comfort": 0.123, "practicality": 0.226}}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3396</v>
+        <v>0.2916</v>
       </c>
       <c r="F18" t="n">
-        <v>0.35702</v>
+        <v>0.32104</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5264800000000001</v>
+        <v>0.47694</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8145200000000001</v>
+        <v>0.79488</v>
       </c>
       <c r="I18" t="n">
-        <v>0.16968</v>
+        <v>0.22426</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9282</v>
       </c>
     </row>
     <row r="19">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
+          <t>{"HVAC": {"energy_cost": 0.337, "environmental": 0.315, "comfort": 0.278, "practicality": 0.07}, "Appliance": {"energy_cost": 0.19, "environmental": 0.467, "comfort": 0.124, "practicality": 0.219}, "Shower": {"energy_cost": 0.333, "environmental": 0.318, "comfort": 0.123, "practicality": 0.226}}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9282</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9323</v>
+        <v>0.9384599999999998</v>
       </c>
       <c r="G19" t="n">
-        <v>0.95074</v>
+        <v>0.9620599999999999</v>
       </c>
       <c r="H19" t="n">
         <v>0.9949</v>
       </c>
       <c r="I19" t="n">
-        <v>0.16968</v>
+        <v>0.22426</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9282</v>
       </c>
     </row>
   </sheetData>
